--- a/data/trans_bre/P1413-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1413-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,68</t>
+          <t>19,95</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 7,22</t>
+          <t>-0,25; 7,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 14,5</t>
+          <t>7,92; 14,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 13,28</t>
+          <t>5,65; 13,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 23,11</t>
+          <t>15,59; 24,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 29,62</t>
+          <t>-0,62; 30,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,27; 104,72</t>
+          <t>44,22; 108,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,15; 115,65</t>
+          <t>36,34; 113,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,13; 78,19</t>
+          <t>45,57; 85,81</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,34</t>
+          <t>8,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>108,09%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,73</t>
+          <t>-0,87; 3,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,88</t>
+          <t>4,58; 8,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,31</t>
+          <t>2,72; 6,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 33,53</t>
+          <t>6,21; 11,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 34,21</t>
+          <t>-6,81; 34,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,67; 147,07</t>
+          <t>60,17; 151,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,35; 103,02</t>
+          <t>34,81; 105,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,83; 272,76</t>
+          <t>33,73; 70,48</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,34</t>
+          <t>8,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,46</t>
+          <t>-4,62; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,5</t>
+          <t>2,97; 10,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,09</t>
+          <t>-2,35; 3,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 12,1</t>
+          <t>4,68; 12,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 40,98</t>
+          <t>-36,48; 37,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,04; 332,35</t>
+          <t>48,04; 337,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 90,02</t>
+          <t>-27,77; 85,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,94; 111,76</t>
+          <t>30,43; 109,1</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>12,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,84</t>
+          <t>1,32; 4,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,88</t>
+          <t>7,48; 10,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,35</t>
+          <t>4,14; 7,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 28,0</t>
+          <t>10,38; 13,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 32,62</t>
+          <t>7,52; 31,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,16; 130,17</t>
+          <t>77,95; 129,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,28; 98,68</t>
+          <t>46,82; 96,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,1; 171,74</t>
+          <t>52,84; 79,02</t>
         </is>
       </c>
     </row>
